--- a/INSTANCES/instances_xlsx/A_MTN_3/334FL_15A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/334FL_15A_1.xlsx
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -10756,7 +10756,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10824,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -10841,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -10892,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10909,7 +10909,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -10926,7 +10926,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
